--- a/diseases/d168/2026-2029.xlsx
+++ b/diseases/d168/2026-2029.xlsx
@@ -21701,12 +21701,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -21731,12 +21731,12 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N119" t="n">
@@ -21745,6 +21745,9 @@
       <c r="O119" t="n">
         <v>0</v>
       </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
       <c r="R119" t="n">
         <v>0</v>
       </c>
@@ -21755,12 +21758,12 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -21780,7 +21783,7 @@
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
       <c r="AT119" t="n">
@@ -21793,42 +21796,42 @@
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21860,12 +21863,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -21890,12 +21893,12 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N120" t="n">
@@ -21904,24 +21907,27 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
+      <c r="P120" t="n">
+        <v>0</v>
+      </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>Rubella congenital</t>
+          <t>Congenital rubella syndrome</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
@@ -21936,7 +21942,7 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
@@ -21946,7 +21952,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD120" t="inlineStr">
@@ -21986,7 +21992,7 @@
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Australia NINDSS congenital rubella notifications.</t>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
         </is>
       </c>
       <c r="AM120" t="inlineStr">
@@ -22014,7 +22020,7 @@
       </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
       <c r="AT120" t="n">
@@ -22027,42 +22033,42 @@
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22094,118 +22100,511 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP121" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="AT121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0</v>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>Rubella congenital</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital rubella notifications.</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN122" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="AT122" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="G123" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>D168</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
         <is>
           <t>先天性风疹综合征</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
+      <c r="K123" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
+      <c r="L123" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr">
+      <c r="M123" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N121" t="n">
-        <v>0</v>
-      </c>
-      <c r="O121" t="n">
-        <v>0</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" t="inlineStr">
+      <c r="N123" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0</v>
+      </c>
+      <c r="S123" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO121" t="inlineStr">
+      <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP121" t="inlineStr">
+      <c r="AP123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR121" t="inlineStr">
+      <c r="AR123" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS121" t="inlineStr"/>
-      <c r="AT121" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU121" t="inlineStr">
+      <c r="AS123" t="inlineStr"/>
+      <c r="AT123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU123" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV121" t="inlineStr">
+      <c r="AV123" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW121" t="inlineStr">
+      <c r="AW123" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX121" t="inlineStr">
+      <c r="AX123" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY121" t="inlineStr">
+      <c r="AY123" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ121" t="inlineStr">
+      <c r="AZ123" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA121" t="inlineStr">
+      <c r="BA123" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB121" t="inlineStr">
+      <c r="BB123" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC121" t="inlineStr">
+      <c r="BC123" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -22327,7 +22726,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10">
@@ -22337,7 +22736,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11">
@@ -22357,7 +22756,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d168/2026-2029.xlsx
+++ b/diseases/d168/2026-2029.xlsx
@@ -11891,7 +11891,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -18721,7 +18721,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -22390,7 +22390,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN122" t="b">

--- a/diseases/d168/2026-2029.xlsx
+++ b/diseases/d168/2026-2029.xlsx
@@ -22610,6 +22610,405 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN125" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22643,7 +23042,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -22726,7 +23125,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -22736,7 +23135,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11">
@@ -22756,7 +23155,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d168/2026-2029.xlsx
+++ b/diseases/d168/2026-2029.xlsx
@@ -1445,7 +1445,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9188,7 +9188,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11488,7 +11488,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11881,7 +11881,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13706,7 +13706,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -14903,7 +14903,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -15296,7 +15296,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17121,7 +17121,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -17520,7 +17520,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -18318,7 +18318,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -18711,7 +18711,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -19960,12 +19960,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -20038,42 +20038,42 @@
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -20105,12 +20105,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -20135,7 +20135,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -20149,9 +20149,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="P111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -20160,82 +20157,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ111" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -20262,7 +20245,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -20314,98 +20297,23 @@
       <c r="P112" t="n">
         <v>0</v>
       </c>
+      <c r="R112" t="n">
+        <v>0</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U112" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD112" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE112" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF112" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG112" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH112" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN112" t="b">
-        <v>1</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -20499,7 +20407,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -20534,7 +20442,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -20551,23 +20459,98 @@
       <c r="P113" t="n">
         <v>0</v>
       </c>
-      <c r="R113" t="n">
-        <v>0</v>
-      </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U113" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG113" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN113" t="b">
+        <v>1</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -20661,7 +20644,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -20713,98 +20696,23 @@
       <c r="P114" t="n">
         <v>0</v>
       </c>
+      <c r="R114" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U114" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
-      <c r="V114" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W114" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X114" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y114" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD114" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE114" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF114" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG114" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH114" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM114" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN114" t="b">
-        <v>1</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -20898,7 +20806,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -20933,7 +20841,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -20950,23 +20858,98 @@
       <c r="P115" t="n">
         <v>0</v>
       </c>
-      <c r="R115" t="n">
-        <v>0</v>
-      </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U115" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD115" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG115" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH115" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM115" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN115" t="b">
+        <v>1</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -21060,7 +21043,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -21112,98 +21095,23 @@
       <c r="P116" t="n">
         <v>0</v>
       </c>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U116" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
-      <c r="V116" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W116" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X116" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y116" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD116" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE116" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF116" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG116" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN116" t="b">
-        <v>1</v>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
@@ -21297,7 +21205,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -21332,7 +21240,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -21349,23 +21257,98 @@
       <c r="P117" t="n">
         <v>0</v>
       </c>
-      <c r="R117" t="n">
-        <v>0</v>
-      </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U117" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN117" t="b">
+        <v>1</v>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
@@ -21459,7 +21442,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -21511,98 +21494,23 @@
       <c r="P118" t="n">
         <v>0</v>
       </c>
+      <c r="R118" t="n">
+        <v>0</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U118" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
-      <c r="V118" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W118" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD118" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE118" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF118" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG118" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN118" t="b">
-        <v>1</v>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
@@ -21696,7 +21604,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -21731,7 +21639,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -21748,23 +21656,98 @@
       <c r="P119" t="n">
         <v>0</v>
       </c>
-      <c r="R119" t="n">
-        <v>0</v>
-      </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U119" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD119" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG119" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH119" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM119" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN119" t="b">
+        <v>1</v>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
@@ -21858,7 +21841,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -21910,98 +21893,23 @@
       <c r="P120" t="n">
         <v>0</v>
       </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U120" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X120" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD120" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE120" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF120" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG120" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN120" t="b">
-        <v>1</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -22095,17 +22003,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -22130,12 +22038,12 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N121" t="n">
@@ -22144,23 +22052,101 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="R121" t="n">
-        <v>0</v>
-      </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P121" t="n">
+        <v>0</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN121" t="b">
+        <v>1</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -22179,7 +22165,7 @@
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
       <c r="AT121" t="n">
@@ -22192,42 +22178,42 @@
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22254,7 +22240,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -22303,98 +22289,23 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
+      <c r="R122" t="n">
+        <v>0</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U122" t="inlineStr">
         <is>
           <t>SER_AU_CONGENITAL_RUBELLA</t>
         </is>
       </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W122" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>Rubella congenital</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD122" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE122" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF122" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG122" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Australia NINDSS congenital rubella notifications.</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN122" t="b">
-        <v>1</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -22488,17 +22399,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -22537,76 +22448,165 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="R123" t="n">
-        <v>0</v>
-      </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Rubella congenital</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital rubella notifications.</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN123" t="b">
+        <v>1</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
       <c r="AT123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -22638,12 +22638,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -22668,7 +22668,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -22682,9 +22682,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="P124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -22693,82 +22690,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA124" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ124" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -22795,7 +22778,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -22847,98 +22830,23 @@
       <c r="P125" t="n">
         <v>0</v>
       </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U125" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
-      <c r="V125" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X125" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y125" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z125" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD125" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE125" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF125" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG125" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM125" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN125" t="b">
-        <v>1</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -23004,6 +22912,642 @@
         </is>
       </c>
       <c r="BC125" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG126" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM126" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN126" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT126" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG128" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM128" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN128" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ128" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -23042,7 +23586,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -23125,7 +23669,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10">
@@ -23135,7 +23679,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11">
@@ -23155,7 +23699,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d168/2026-2029.xlsx
+++ b/diseases/d168/2026-2029.xlsx
@@ -23553,6 +23553,550 @@
         </is>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT129" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN130" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT130" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC130" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP131" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS131" t="inlineStr"/>
+      <c r="AT131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU131" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV131" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA131" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB131" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC131" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23586,7 +24130,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -23669,7 +24213,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -23679,7 +24223,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11">
@@ -23699,7 +24243,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d168/2026-2029.xlsx
+++ b/diseases/d168/2026-2029.xlsx
@@ -3920,6 +3920,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4065,6 +4070,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4201,6 +4211,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4337,6 +4352,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4473,6 +4493,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4609,6 +4634,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4745,6 +4775,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4881,6 +4916,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5017,6 +5057,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5153,6 +5198,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5289,6 +5339,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5425,6 +5480,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5561,6 +5621,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5697,6 +5762,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5833,6 +5903,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5969,6 +6044,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6105,6 +6185,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6241,6 +6326,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6377,6 +6467,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6513,6 +6608,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6649,6 +6749,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6785,6 +6890,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6921,6 +7031,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7057,6 +7172,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7193,6 +7313,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7329,6 +7454,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7465,6 +7595,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7601,6 +7736,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7737,6 +7877,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7882,6 +8027,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12779,6 +12929,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12924,6 +13079,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13060,6 +13220,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13196,6 +13361,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13332,6 +13502,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13468,6 +13643,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13604,6 +13784,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13740,6 +13925,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13876,6 +14066,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14012,6 +14207,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14148,6 +14348,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14284,6 +14489,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14420,6 +14630,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14556,6 +14771,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14692,6 +14912,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14828,6 +15053,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14964,6 +15194,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15100,6 +15335,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15236,6 +15476,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15372,6 +15617,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15508,6 +15758,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15644,6 +15899,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15780,6 +16040,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15916,6 +16181,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16052,6 +16322,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16188,6 +16463,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16324,6 +16604,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16460,6 +16745,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16596,6 +16886,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17143,6 +17438,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21641,6 +21941,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21786,6 +22091,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21922,6 +22232,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22058,6 +22373,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22194,6 +22514,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22330,6 +22655,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22466,6 +22796,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22602,6 +22937,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22738,6 +23078,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22874,6 +23219,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23010,6 +23360,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23146,6 +23501,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23282,6 +23642,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23418,6 +23783,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23554,6 +23924,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23690,6 +24065,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23826,6 +24206,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23962,6 +24347,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24098,6 +24488,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24234,6 +24629,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24370,6 +24770,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24506,6 +24911,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24642,6 +25052,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24778,6 +25193,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24914,6 +25334,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25050,6 +25475,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25186,6 +25616,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25322,6 +25757,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25458,6 +25898,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26005,6 +26450,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30902,6 +31352,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31047,6 +31502,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31183,6 +31643,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31319,6 +31784,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31455,6 +31925,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31591,6 +32066,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31727,6 +32207,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31863,6 +32348,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31999,6 +32489,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32135,6 +32630,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32271,6 +32771,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32407,6 +32912,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32543,6 +33053,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32679,6 +33194,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32815,6 +33335,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32951,6 +33476,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33087,6 +33617,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33223,6 +33758,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33359,6 +33899,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33495,6 +34040,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33631,6 +34181,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33767,6 +34322,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33903,6 +34463,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34039,6 +34604,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34175,6 +34745,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34311,6 +34886,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34447,6 +35027,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34583,6 +35168,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34719,6 +35309,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34864,6 +35459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39761,6 +40361,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39906,6 +40511,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45598,6 +46208,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45743,6 +46358,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO267" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51021,6 +51641,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO294" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51166,6 +51791,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO295" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56392,12 +57022,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -56431,17 +57061,22 @@
         </is>
       </c>
       <c r="N322" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O322" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R322" t="n">
-        <v>0</v>
+        <v>0.002800964172162365</v>
       </c>
       <c r="S322" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO322" t="inlineStr">
@@ -56470,42 +57105,42 @@
       </c>
       <c r="AV322" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW322" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX322" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY322" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ322" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA322" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB322" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC322" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -56537,12 +57172,12 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -56587,6 +57222,11 @@
       <c r="S323" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO323" t="inlineStr">
@@ -56615,42 +57255,42 @@
       </c>
       <c r="AV323" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW323" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX323" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY323" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ323" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA323" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB323" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC323" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -56682,12 +57322,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -56712,7 +57352,7 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
@@ -56726,9 +57366,6 @@
       <c r="O324" t="n">
         <v>0</v>
       </c>
-      <c r="P324" t="n">
-        <v>0</v>
-      </c>
       <c r="R324" t="n">
         <v>0</v>
       </c>
@@ -56737,82 +57374,73 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
       <c r="AA324" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO324" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP324" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ324" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS324" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR324" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS324" t="inlineStr"/>
       <c r="AT324" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU324" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV324" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW324" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX324" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY324" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ324" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA324" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB324" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC324" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -56839,7 +57467,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -56891,98 +57519,23 @@
       <c r="P325" t="n">
         <v>0</v>
       </c>
+      <c r="R325" t="n">
+        <v>0</v>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U325" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
-      <c r="V325" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W325" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X325" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y325" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z325" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA325" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB325" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC325" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD325" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE325" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF325" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG325" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH325" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI325" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ325" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK325" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM325" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN325" t="b">
-        <v>1</v>
       </c>
       <c r="AO325" t="inlineStr">
         <is>
@@ -57076,7 +57629,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -57111,7 +57664,7 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -57128,23 +57681,98 @@
       <c r="P326" t="n">
         <v>0</v>
       </c>
-      <c r="R326" t="n">
-        <v>0</v>
-      </c>
-      <c r="S326" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U326" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W326" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X326" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y326" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z326" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA326" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB326" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC326" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD326" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE326" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF326" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG326" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH326" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI326" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ326" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK326" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM326" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN326" t="b">
+        <v>1</v>
       </c>
       <c r="AO326" t="inlineStr">
         <is>
@@ -57238,7 +57866,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -57290,98 +57918,23 @@
       <c r="P327" t="n">
         <v>0</v>
       </c>
+      <c r="R327" t="n">
+        <v>0</v>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U327" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
-      <c r="V327" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W327" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X327" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y327" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z327" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA327" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB327" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC327" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD327" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE327" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF327" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG327" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH327" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI327" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ327" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK327" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM327" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN327" t="b">
-        <v>1</v>
       </c>
       <c r="AO327" t="inlineStr">
         <is>
@@ -57475,7 +58028,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -57510,7 +58063,7 @@
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
@@ -57527,23 +58080,98 @@
       <c r="P328" t="n">
         <v>0</v>
       </c>
-      <c r="R328" t="n">
-        <v>0</v>
-      </c>
-      <c r="S328" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U328" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W328" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X328" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y328" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z328" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA328" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB328" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC328" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD328" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE328" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF328" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG328" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH328" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI328" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ328" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK328" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM328" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN328" t="b">
+        <v>1</v>
       </c>
       <c r="AO328" t="inlineStr">
         <is>
@@ -57637,7 +58265,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -57689,98 +58317,23 @@
       <c r="P329" t="n">
         <v>0</v>
       </c>
+      <c r="R329" t="n">
+        <v>0</v>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U329" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
-      <c r="V329" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W329" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X329" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y329" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z329" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA329" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB329" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC329" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD329" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE329" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF329" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG329" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH329" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI329" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ329" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK329" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM329" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN329" t="b">
-        <v>1</v>
       </c>
       <c r="AO329" t="inlineStr">
         <is>
@@ -57874,7 +58427,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -57909,7 +58462,7 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -57926,23 +58479,98 @@
       <c r="P330" t="n">
         <v>0</v>
       </c>
-      <c r="R330" t="n">
-        <v>0</v>
-      </c>
-      <c r="S330" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U330" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
+      <c r="V330" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W330" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X330" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y330" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z330" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA330" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB330" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC330" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD330" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE330" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF330" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG330" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH330" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI330" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ330" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK330" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM330" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN330" t="b">
+        <v>1</v>
       </c>
       <c r="AO330" t="inlineStr">
         <is>
@@ -58036,7 +58664,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -58088,98 +58716,23 @@
       <c r="P331" t="n">
         <v>0</v>
       </c>
+      <c r="R331" t="n">
+        <v>0</v>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U331" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
-      <c r="V331" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W331" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X331" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y331" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z331" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA331" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB331" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC331" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD331" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE331" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF331" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG331" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH331" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI331" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ331" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK331" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM331" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN331" t="b">
-        <v>1</v>
       </c>
       <c r="AO331" t="inlineStr">
         <is>
@@ -58273,7 +58826,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -58308,7 +58861,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
@@ -58325,23 +58878,98 @@
       <c r="P332" t="n">
         <v>0</v>
       </c>
-      <c r="R332" t="n">
-        <v>0</v>
-      </c>
-      <c r="S332" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U332" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
+      <c r="V332" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W332" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X332" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y332" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z332" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA332" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB332" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC332" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD332" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE332" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF332" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG332" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH332" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI332" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ332" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK332" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM332" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN332" t="b">
+        <v>1</v>
       </c>
       <c r="AO332" t="inlineStr">
         <is>
@@ -58435,7 +59063,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -58487,98 +59115,23 @@
       <c r="P333" t="n">
         <v>0</v>
       </c>
+      <c r="R333" t="n">
+        <v>0</v>
+      </c>
+      <c r="S333" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U333" t="inlineStr">
         <is>
           <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
-      <c r="V333" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W333" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X333" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y333" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z333" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA333" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB333" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC333" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD333" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE333" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF333" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG333" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH333" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI333" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ333" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK333" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM333" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN333" t="b">
-        <v>1</v>
       </c>
       <c r="AO333" t="inlineStr">
         <is>
@@ -58672,17 +59225,17 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -58707,12 +59260,12 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N334" t="n">
@@ -58721,23 +59274,101 @@
       <c r="O334" t="n">
         <v>0</v>
       </c>
-      <c r="R334" t="n">
-        <v>0</v>
-      </c>
-      <c r="S334" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P334" t="n">
+        <v>0</v>
       </c>
       <c r="U334" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V334" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W334" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X334" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y334" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z334" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB334" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC334" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD334" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE334" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF334" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG334" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH334" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI334" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ334" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK334" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM334" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN334" t="b">
+        <v>1</v>
       </c>
       <c r="AO334" t="inlineStr">
         <is>
@@ -58756,7 +59387,7 @@
       </c>
       <c r="AS334" t="inlineStr">
         <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
         </is>
       </c>
       <c r="AT334" t="n">
@@ -58769,42 +59400,42 @@
       </c>
       <c r="AV334" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW334" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX334" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY334" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ334" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA334" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB334" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC334" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -58831,7 +59462,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -58880,98 +59511,23 @@
       <c r="O335" t="n">
         <v>0</v>
       </c>
+      <c r="R335" t="n">
+        <v>0</v>
+      </c>
+      <c r="S335" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U335" t="inlineStr">
         <is>
           <t>SER_AU_CONGENITAL_RUBELLA</t>
         </is>
       </c>
-      <c r="V335" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W335" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X335" t="inlineStr">
-        <is>
-          <t>Rubella congenital</t>
-        </is>
-      </c>
-      <c r="Y335" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z335" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA335" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB335" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC335" t="inlineStr">
-        <is>
-          <t>country:AU:national</t>
-        </is>
-      </c>
-      <c r="AD335" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE335" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF335" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG335" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH335" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI335" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ335" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK335" t="inlineStr">
-        <is>
-          <t>Australia NINDSS congenital rubella notifications.</t>
-        </is>
-      </c>
-      <c r="AM335" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN335" t="b">
-        <v>1</v>
       </c>
       <c r="AO335" t="inlineStr">
         <is>
@@ -59065,17 +59621,17 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -59114,23 +59670,98 @@
       <c r="O336" t="n">
         <v>0</v>
       </c>
-      <c r="R336" t="n">
-        <v>0</v>
-      </c>
-      <c r="S336" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="U336" t="inlineStr">
         <is>
           <t>SER_AU_CONGENITAL_RUBELLA</t>
         </is>
       </c>
+      <c r="V336" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W336" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X336" t="inlineStr">
+        <is>
+          <t>Rubella congenital</t>
+        </is>
+      </c>
+      <c r="Y336" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z336" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA336" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
+      </c>
+      <c r="AB336" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC336" t="inlineStr">
+        <is>
+          <t>country:AU:national</t>
+        </is>
+      </c>
+      <c r="AD336" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE336" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF336" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG336" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH336" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI336" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ336" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK336" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital rubella notifications.</t>
+        </is>
+      </c>
+      <c r="AM336" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN336" t="b">
+        <v>1</v>
       </c>
       <c r="AO336" t="inlineStr">
         <is>
@@ -59167,12 +59798,12 @@
       </c>
       <c r="AW336" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX336" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY336" t="inlineStr">
@@ -59187,12 +59818,12 @@
       </c>
       <c r="BA336" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB336" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC336" t="inlineStr">
@@ -59224,7 +59855,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -59273,98 +59904,23 @@
       <c r="O337" t="n">
         <v>0</v>
       </c>
+      <c r="R337" t="n">
+        <v>0</v>
+      </c>
+      <c r="S337" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="U337" t="inlineStr">
         <is>
           <t>SER_AU_CONGENITAL_RUBELLA</t>
         </is>
       </c>
-      <c r="V337" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W337" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X337" t="inlineStr">
-        <is>
-          <t>Rubella congenital</t>
-        </is>
-      </c>
-      <c r="Y337" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z337" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA337" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB337" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC337" t="inlineStr">
-        <is>
-          <t>country:AU-ACT:national</t>
-        </is>
-      </c>
-      <c r="AD337" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE337" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF337" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG337" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH337" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI337" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ337" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK337" t="inlineStr">
-        <is>
-          <t>Australia NINDSS congenital rubella notifications.</t>
-        </is>
-      </c>
-      <c r="AM337" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN337" t="b">
-        <v>1</v>
       </c>
       <c r="AO337" t="inlineStr">
         <is>
@@ -59458,17 +60014,17 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -59507,27 +60063,102 @@
       <c r="O338" t="n">
         <v>0</v>
       </c>
-      <c r="R338" t="n">
-        <v>0</v>
-      </c>
-      <c r="S338" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="U338" t="inlineStr">
         <is>
           <t>SER_AU_CONGENITAL_RUBELLA</t>
         </is>
       </c>
+      <c r="V338" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W338" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X338" t="inlineStr">
+        <is>
+          <t>Rubella congenital</t>
+        </is>
+      </c>
+      <c r="Y338" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z338" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA338" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB338" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC338" t="inlineStr">
+        <is>
+          <t>country:AU-ACT:national</t>
+        </is>
+      </c>
+      <c r="AD338" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE338" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF338" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG338" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH338" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI338" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ338" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK338" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital rubella notifications.</t>
+        </is>
+      </c>
+      <c r="AM338" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN338" t="b">
+        <v>1</v>
+      </c>
       <c r="AO338" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP338" t="inlineStr">
@@ -59537,7 +60168,7 @@
       </c>
       <c r="AQ338" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS338" t="inlineStr">
@@ -59550,7 +60181,7 @@
       </c>
       <c r="AU338" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV338" t="inlineStr">
@@ -59560,7 +60191,7 @@
       </c>
       <c r="AW338" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX338" t="inlineStr">
@@ -59580,7 +60211,7 @@
       </c>
       <c r="BA338" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB338" t="inlineStr">
@@ -59617,7 +60248,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -59666,98 +60297,23 @@
       <c r="O339" t="n">
         <v>0</v>
       </c>
+      <c r="R339" t="n">
+        <v>0</v>
+      </c>
+      <c r="S339" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="U339" t="inlineStr">
         <is>
           <t>SER_AU_CONGENITAL_RUBELLA</t>
         </is>
       </c>
-      <c r="V339" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W339" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X339" t="inlineStr">
-        <is>
-          <t>Rubella congenital</t>
-        </is>
-      </c>
-      <c r="Y339" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z339" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA339" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB339" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC339" t="inlineStr">
-        <is>
-          <t>country:AU-NSW:national</t>
-        </is>
-      </c>
-      <c r="AD339" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE339" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF339" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG339" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH339" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI339" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ339" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK339" t="inlineStr">
-        <is>
-          <t>Australia NINDSS congenital rubella notifications.</t>
-        </is>
-      </c>
-      <c r="AM339" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN339" t="b">
-        <v>1</v>
       </c>
       <c r="AO339" t="inlineStr">
         <is>
@@ -59851,17 +60407,17 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -59900,23 +60456,98 @@
       <c r="O340" t="n">
         <v>0</v>
       </c>
-      <c r="R340" t="n">
-        <v>0</v>
-      </c>
-      <c r="S340" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="U340" t="inlineStr">
         <is>
           <t>SER_AU_CONGENITAL_RUBELLA</t>
         </is>
       </c>
+      <c r="V340" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W340" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X340" t="inlineStr">
+        <is>
+          <t>Rubella congenital</t>
+        </is>
+      </c>
+      <c r="Y340" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z340" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA340" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
+      </c>
+      <c r="AB340" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC340" t="inlineStr">
+        <is>
+          <t>country:AU-NSW:national</t>
+        </is>
+      </c>
+      <c r="AD340" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE340" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF340" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG340" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH340" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI340" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ340" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK340" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital rubella notifications.</t>
+        </is>
+      </c>
+      <c r="AM340" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN340" t="b">
+        <v>1</v>
       </c>
       <c r="AO340" t="inlineStr">
         <is>
@@ -59953,7 +60584,7 @@
       </c>
       <c r="AW340" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX340" t="inlineStr">
@@ -59973,7 +60604,7 @@
       </c>
       <c r="BA340" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB340" t="inlineStr">
@@ -60010,7 +60641,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
@@ -60059,98 +60690,23 @@
       <c r="O341" t="n">
         <v>0</v>
       </c>
+      <c r="R341" t="n">
+        <v>0</v>
+      </c>
+      <c r="S341" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="U341" t="inlineStr">
         <is>
           <t>SER_AU_CONGENITAL_RUBELLA</t>
         </is>
       </c>
-      <c r="V341" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W341" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X341" t="inlineStr">
-        <is>
-          <t>Rubella congenital</t>
-        </is>
-      </c>
-      <c r="Y341" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z341" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA341" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB341" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC341" t="inlineStr">
-        <is>
-          <t>country:AU-NT:national</t>
-        </is>
-      </c>
-      <c r="AD341" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE341" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF341" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG341" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH341" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI341" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ341" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK341" t="inlineStr">
-        <is>
-          <t>Australia NINDSS congenital rubella notifications.</t>
-        </is>
-      </c>
-      <c r="AM341" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN341" t="b">
-        <v>1</v>
       </c>
       <c r="AO341" t="inlineStr">
         <is>
@@ -60244,17 +60800,17 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -60293,23 +60849,98 @@
       <c r="O342" t="n">
         <v>0</v>
       </c>
-      <c r="R342" t="n">
-        <v>0</v>
-      </c>
-      <c r="S342" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="U342" t="inlineStr">
         <is>
           <t>SER_AU_CONGENITAL_RUBELLA</t>
         </is>
       </c>
+      <c r="V342" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W342" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X342" t="inlineStr">
+        <is>
+          <t>Rubella congenital</t>
+        </is>
+      </c>
+      <c r="Y342" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z342" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA342" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
+      </c>
+      <c r="AB342" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC342" t="inlineStr">
+        <is>
+          <t>country:AU-NT:national</t>
+        </is>
+      </c>
+      <c r="AD342" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE342" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF342" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG342" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH342" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI342" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ342" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK342" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital rubella notifications.</t>
+        </is>
+      </c>
+      <c r="AM342" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN342" t="b">
+        <v>1</v>
       </c>
       <c r="AO342" t="inlineStr">
         <is>
@@ -60346,7 +60977,7 @@
       </c>
       <c r="AW342" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX342" t="inlineStr">
@@ -60366,7 +60997,7 @@
       </c>
       <c r="BA342" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB342" t="inlineStr">
@@ -60403,7 +61034,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -60452,98 +61083,23 @@
       <c r="O343" t="n">
         <v>0</v>
       </c>
+      <c r="R343" t="n">
+        <v>0</v>
+      </c>
+      <c r="S343" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="U343" t="inlineStr">
         <is>
           <t>SER_AU_CONGENITAL_RUBELLA</t>
         </is>
       </c>
-      <c r="V343" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W343" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X343" t="inlineStr">
-        <is>
-          <t>Rubella congenital</t>
-        </is>
-      </c>
-      <c r="Y343" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z343" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA343" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB343" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC343" t="inlineStr">
-        <is>
-          <t>country:AU-QLD:national</t>
-        </is>
-      </c>
-      <c r="AD343" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE343" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF343" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG343" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH343" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI343" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ343" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK343" t="inlineStr">
-        <is>
-          <t>Australia NINDSS congenital rubella notifications.</t>
-        </is>
-      </c>
-      <c r="AM343" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN343" t="b">
-        <v>1</v>
       </c>
       <c r="AO343" t="inlineStr">
         <is>
@@ -60637,17 +61193,17 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -60686,23 +61242,98 @@
       <c r="O344" t="n">
         <v>0</v>
       </c>
-      <c r="R344" t="n">
-        <v>0</v>
-      </c>
-      <c r="S344" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="U344" t="inlineStr">
         <is>
           <t>SER_AU_CONGENITAL_RUBELLA</t>
         </is>
       </c>
+      <c r="V344" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W344" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X344" t="inlineStr">
+        <is>
+          <t>Rubella congenital</t>
+        </is>
+      </c>
+      <c r="Y344" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z344" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA344" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
+      </c>
+      <c r="AB344" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC344" t="inlineStr">
+        <is>
+          <t>country:AU-QLD:national</t>
+        </is>
+      </c>
+      <c r="AD344" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE344" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF344" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG344" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH344" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI344" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ344" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK344" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital rubella notifications.</t>
+        </is>
+      </c>
+      <c r="AM344" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN344" t="b">
+        <v>1</v>
       </c>
       <c r="AO344" t="inlineStr">
         <is>
@@ -60739,7 +61370,7 @@
       </c>
       <c r="AW344" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX344" t="inlineStr">
@@ -60759,7 +61390,7 @@
       </c>
       <c r="BA344" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB344" t="inlineStr">
@@ -60796,7 +61427,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -60845,98 +61476,23 @@
       <c r="O345" t="n">
         <v>0</v>
       </c>
+      <c r="R345" t="n">
+        <v>0</v>
+      </c>
+      <c r="S345" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="U345" t="inlineStr">
         <is>
           <t>SER_AU_CONGENITAL_RUBELLA</t>
         </is>
       </c>
-      <c r="V345" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W345" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X345" t="inlineStr">
-        <is>
-          <t>Rubella congenital</t>
-        </is>
-      </c>
-      <c r="Y345" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z345" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA345" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB345" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC345" t="inlineStr">
-        <is>
-          <t>country:AU-SA:national</t>
-        </is>
-      </c>
-      <c r="AD345" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE345" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF345" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG345" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH345" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI345" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ345" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK345" t="inlineStr">
-        <is>
-          <t>Australia NINDSS congenital rubella notifications.</t>
-        </is>
-      </c>
-      <c r="AM345" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN345" t="b">
-        <v>1</v>
       </c>
       <c r="AO345" t="inlineStr">
         <is>
@@ -61030,17 +61586,17 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -61079,27 +61635,102 @@
       <c r="O346" t="n">
         <v>0</v>
       </c>
-      <c r="R346" t="n">
-        <v>0</v>
-      </c>
-      <c r="S346" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="U346" t="inlineStr">
         <is>
           <t>SER_AU_CONGENITAL_RUBELLA</t>
         </is>
       </c>
+      <c r="V346" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W346" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X346" t="inlineStr">
+        <is>
+          <t>Rubella congenital</t>
+        </is>
+      </c>
+      <c r="Y346" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z346" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA346" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB346" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC346" t="inlineStr">
+        <is>
+          <t>country:AU-SA:national</t>
+        </is>
+      </c>
+      <c r="AD346" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE346" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF346" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG346" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH346" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI346" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ346" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK346" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital rubella notifications.</t>
+        </is>
+      </c>
+      <c r="AM346" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN346" t="b">
+        <v>1</v>
+      </c>
       <c r="AO346" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP346" t="inlineStr">
@@ -61109,7 +61740,7 @@
       </c>
       <c r="AQ346" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS346" t="inlineStr">
@@ -61122,7 +61753,7 @@
       </c>
       <c r="AU346" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV346" t="inlineStr">
@@ -61132,7 +61763,7 @@
       </c>
       <c r="AW346" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX346" t="inlineStr">
@@ -61152,7 +61783,7 @@
       </c>
       <c r="BA346" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB346" t="inlineStr">
@@ -61189,7 +61820,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -61238,98 +61869,23 @@
       <c r="O347" t="n">
         <v>0</v>
       </c>
+      <c r="R347" t="n">
+        <v>0</v>
+      </c>
+      <c r="S347" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="U347" t="inlineStr">
         <is>
           <t>SER_AU_CONGENITAL_RUBELLA</t>
         </is>
       </c>
-      <c r="V347" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W347" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X347" t="inlineStr">
-        <is>
-          <t>Rubella congenital</t>
-        </is>
-      </c>
-      <c r="Y347" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z347" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA347" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB347" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC347" t="inlineStr">
-        <is>
-          <t>country:AU-TAS:national</t>
-        </is>
-      </c>
-      <c r="AD347" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE347" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF347" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG347" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH347" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI347" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ347" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK347" t="inlineStr">
-        <is>
-          <t>Australia NINDSS congenital rubella notifications.</t>
-        </is>
-      </c>
-      <c r="AM347" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN347" t="b">
-        <v>1</v>
       </c>
       <c r="AO347" t="inlineStr">
         <is>
@@ -61423,17 +61979,17 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -61472,27 +62028,102 @@
       <c r="O348" t="n">
         <v>0</v>
       </c>
-      <c r="R348" t="n">
-        <v>0</v>
-      </c>
-      <c r="S348" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="U348" t="inlineStr">
         <is>
           <t>SER_AU_CONGENITAL_RUBELLA</t>
         </is>
       </c>
+      <c r="V348" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W348" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X348" t="inlineStr">
+        <is>
+          <t>Rubella congenital</t>
+        </is>
+      </c>
+      <c r="Y348" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z348" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA348" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB348" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC348" t="inlineStr">
+        <is>
+          <t>country:AU-TAS:national</t>
+        </is>
+      </c>
+      <c r="AD348" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE348" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF348" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG348" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH348" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI348" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ348" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK348" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital rubella notifications.</t>
+        </is>
+      </c>
+      <c r="AM348" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN348" t="b">
+        <v>1</v>
+      </c>
       <c r="AO348" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP348" t="inlineStr">
@@ -61502,7 +62133,7 @@
       </c>
       <c r="AQ348" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS348" t="inlineStr">
@@ -61515,7 +62146,7 @@
       </c>
       <c r="AU348" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV348" t="inlineStr">
@@ -61525,7 +62156,7 @@
       </c>
       <c r="AW348" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX348" t="inlineStr">
@@ -61545,7 +62176,7 @@
       </c>
       <c r="BA348" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB348" t="inlineStr">
@@ -61582,7 +62213,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
@@ -61631,98 +62262,23 @@
       <c r="O349" t="n">
         <v>0</v>
       </c>
+      <c r="R349" t="n">
+        <v>0</v>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="U349" t="inlineStr">
         <is>
           <t>SER_AU_CONGENITAL_RUBELLA</t>
         </is>
       </c>
-      <c r="V349" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W349" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X349" t="inlineStr">
-        <is>
-          <t>Rubella congenital</t>
-        </is>
-      </c>
-      <c r="Y349" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z349" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA349" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB349" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC349" t="inlineStr">
-        <is>
-          <t>country:AU-VIC:national</t>
-        </is>
-      </c>
-      <c r="AD349" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE349" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF349" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG349" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH349" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI349" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ349" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK349" t="inlineStr">
-        <is>
-          <t>Australia NINDSS congenital rubella notifications.</t>
-        </is>
-      </c>
-      <c r="AM349" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN349" t="b">
-        <v>1</v>
       </c>
       <c r="AO349" t="inlineStr">
         <is>
@@ -61816,17 +62372,17 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -61865,27 +62421,102 @@
       <c r="O350" t="n">
         <v>0</v>
       </c>
-      <c r="R350" t="n">
-        <v>0</v>
-      </c>
-      <c r="S350" t="inlineStr">
-        <is>
-          <t>abs_computed</t>
-        </is>
-      </c>
       <c r="U350" t="inlineStr">
         <is>
           <t>SER_AU_CONGENITAL_RUBELLA</t>
         </is>
       </c>
+      <c r="V350" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W350" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X350" t="inlineStr">
+        <is>
+          <t>Rubella congenital</t>
+        </is>
+      </c>
+      <c r="Y350" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z350" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA350" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB350" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC350" t="inlineStr">
+        <is>
+          <t>country:AU-VIC:national</t>
+        </is>
+      </c>
+      <c r="AD350" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE350" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF350" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG350" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH350" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI350" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ350" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK350" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital rubella notifications.</t>
+        </is>
+      </c>
+      <c r="AM350" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN350" t="b">
+        <v>1</v>
+      </c>
       <c r="AO350" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP350" t="inlineStr">
@@ -61895,7 +62526,7 @@
       </c>
       <c r="AQ350" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS350" t="inlineStr">
@@ -61908,7 +62539,7 @@
       </c>
       <c r="AU350" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV350" t="inlineStr">
@@ -61918,7 +62549,7 @@
       </c>
       <c r="AW350" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX350" t="inlineStr">
@@ -61938,7 +62569,7 @@
       </c>
       <c r="BA350" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB350" t="inlineStr">
@@ -61975,7 +62606,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -62024,98 +62655,23 @@
       <c r="O351" t="n">
         <v>0</v>
       </c>
+      <c r="R351" t="n">
+        <v>0</v>
+      </c>
+      <c r="S351" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
+        </is>
+      </c>
       <c r="U351" t="inlineStr">
         <is>
           <t>SER_AU_CONGENITAL_RUBELLA</t>
         </is>
       </c>
-      <c r="V351" t="inlineStr">
-        <is>
-          <t>SER_AU_CONGENITAL_RUBELLA</t>
-        </is>
-      </c>
-      <c r="W351" t="inlineStr">
-        <is>
-          <t>SRC_AU_NINDSS</t>
-        </is>
-      </c>
-      <c r="X351" t="inlineStr">
-        <is>
-          <t>Rubella congenital</t>
-        </is>
-      </c>
-      <c r="Y351" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z351" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA351" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB351" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC351" t="inlineStr">
-        <is>
-          <t>country:AU-WA:national</t>
-        </is>
-      </c>
-      <c r="AD351" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE351" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF351" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG351" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH351" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI351" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ351" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK351" t="inlineStr">
-        <is>
-          <t>Australia NINDSS congenital rubella notifications.</t>
-        </is>
-      </c>
-      <c r="AM351" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN351" t="b">
-        <v>1</v>
       </c>
       <c r="AO351" t="inlineStr">
         <is>
@@ -62209,17 +62765,17 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -62258,76 +62814,165 @@
       <c r="O352" t="n">
         <v>0</v>
       </c>
-      <c r="R352" t="n">
-        <v>0</v>
-      </c>
-      <c r="S352" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="V352" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
+      <c r="W352" t="inlineStr">
+        <is>
+          <t>SRC_AU_NINDSS</t>
+        </is>
+      </c>
+      <c r="X352" t="inlineStr">
+        <is>
+          <t>Rubella congenital</t>
+        </is>
+      </c>
+      <c r="Y352" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z352" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB352" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC352" t="inlineStr">
+        <is>
+          <t>country:AU-WA:national</t>
+        </is>
+      </c>
+      <c r="AD352" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE352" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF352" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG352" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH352" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI352" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ352" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK352" t="inlineStr">
+        <is>
+          <t>Australia NINDSS congenital rubella notifications.</t>
+        </is>
+      </c>
+      <c r="AM352" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN352" t="b">
+        <v>1</v>
       </c>
       <c r="AO352" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP352" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR352" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS352" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ352" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS352" t="inlineStr">
+        <is>
+          <t>SER_AU_CONGENITAL_RUBELLA</t>
+        </is>
+      </c>
       <c r="AT352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU352" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV352" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW352" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX352" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY352" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ352" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA352" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB352" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC352" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -62359,12 +63004,12 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -62389,7 +63034,7 @@
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
@@ -62398,98 +63043,86 @@
         </is>
       </c>
       <c r="N353" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O353" t="n">
-        <v>0</v>
-      </c>
-      <c r="P353" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R353" t="n">
-        <v>0</v>
+        <v>0.0009336547240541215</v>
       </c>
       <c r="S353" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U353" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+          <t>ibge_computed</t>
         </is>
       </c>
       <c r="AA353" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO353" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP353" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ353" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS353" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR353" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS353" t="inlineStr"/>
       <c r="AT353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU353" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV353" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="AW353" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="AX353" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="AY353" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
       <c r="AZ353" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>sinan_datasus</t>
         </is>
       </c>
       <c r="BA353" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Brazil DATASUS SINAN</t>
         </is>
       </c>
       <c r="BB353" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
         </is>
       </c>
       <c r="BC353" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>ftp_dbc</t>
         </is>
       </c>
     </row>
@@ -62516,17 +63149,17 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -62551,7 +63184,7 @@
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
@@ -62565,168 +63198,81 @@
       <c r="O354" t="n">
         <v>0</v>
       </c>
-      <c r="P354" t="n">
-        <v>0</v>
-      </c>
-      <c r="U354" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V354" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W354" t="inlineStr">
-        <is>
-          <t>SRC_JP_NIID</t>
-        </is>
-      </c>
-      <c r="X354" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="Y354" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z354" t="inlineStr">
-        <is>
-          <t>notification</t>
+      <c r="R354" t="n">
+        <v>0</v>
+      </c>
+      <c r="S354" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA354" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB354" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC354" t="inlineStr">
-        <is>
-          <t>country:JP:national</t>
-        </is>
-      </c>
-      <c r="AD354" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE354" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF354" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG354" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH354" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI354" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ354" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
-        </is>
-      </c>
-      <c r="AK354" t="inlineStr">
-        <is>
-          <t>Japan NIID congenital rubella syndrome notifications.</t>
-        </is>
-      </c>
-      <c r="AM354" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN354" t="b">
-        <v>1</v>
+          <t>monthly</t>
+        </is>
       </c>
       <c r="AO354" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP354" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ354" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS354" t="inlineStr">
-        <is>
-          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR354" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS354" t="inlineStr"/>
       <c r="AT354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU354" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV354" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW354" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX354" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY354" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ354" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA354" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB354" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC354" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -62788,7 +63334,7 @@
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
@@ -62950,7 +63496,7 @@
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M356" t="inlineStr">
@@ -63187,7 +63733,7 @@
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M357" t="inlineStr">
@@ -63349,7 +63895,7 @@
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
@@ -63586,7 +64132,7 @@
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
@@ -63748,7 +64294,7 @@
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
@@ -63955,118 +64501,522 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N361" t="n">
+        <v>0</v>
+      </c>
+      <c r="O361" t="n">
+        <v>0</v>
+      </c>
+      <c r="P361" t="n">
+        <v>0</v>
+      </c>
+      <c r="R361" t="n">
+        <v>0</v>
+      </c>
+      <c r="S361" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA361" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO361" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP361" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ361" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS361" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT361" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU361" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV361" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW361" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX361" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY361" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ361" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA361" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB361" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC361" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N362" t="n">
+        <v>0</v>
+      </c>
+      <c r="O362" t="n">
+        <v>0</v>
+      </c>
+      <c r="P362" t="n">
+        <v>0</v>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V362" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W362" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X362" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y362" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z362" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB362" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC362" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD362" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE362" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF362" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG362" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH362" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI362" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ362" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK362" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM362" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN362" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO362" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP362" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ362" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS362" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT362" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU362" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV362" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW362" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX362" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY362" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ362" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA362" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB362" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC362" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G361" t="inlineStr">
+      <c r="G363" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H361" t="inlineStr">
-        <is>
-          <t>D168</t>
-        </is>
-      </c>
-      <c r="I361" t="inlineStr">
-        <is>
-          <t>Congenital rubella syndrome</t>
-        </is>
-      </c>
-      <c r="J361" t="inlineStr">
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
         <is>
           <t>先天性风疹综合征</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr">
+      <c r="K363" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L361" t="inlineStr">
+      <c r="L363" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M361" t="inlineStr">
+      <c r="M363" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N361" t="n">
-        <v>0</v>
-      </c>
-      <c r="O361" t="n">
-        <v>0</v>
-      </c>
-      <c r="R361" t="n">
-        <v>0</v>
-      </c>
-      <c r="S361" t="inlineStr">
+      <c r="N363" t="n">
+        <v>0</v>
+      </c>
+      <c r="O363" t="n">
+        <v>0</v>
+      </c>
+      <c r="R363" t="n">
+        <v>0</v>
+      </c>
+      <c r="S363" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO361" t="inlineStr">
+      <c r="AA363" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO363" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP361" t="inlineStr">
+      <c r="AP363" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR361" t="inlineStr">
+      <c r="AR363" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS361" t="inlineStr"/>
-      <c r="AT361" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU361" t="inlineStr">
+      <c r="AS363" t="inlineStr"/>
+      <c r="AT363" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU363" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV361" t="inlineStr">
+      <c r="AV363" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW361" t="inlineStr">
+      <c r="AW363" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX361" t="inlineStr">
+      <c r="AX363" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY361" t="inlineStr">
+      <c r="AY363" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ361" t="inlineStr">
+      <c r="AZ363" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA361" t="inlineStr">
+      <c r="BA363" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB361" t="inlineStr">
+      <c r="BB363" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC361" t="inlineStr">
+      <c r="BC363" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -64188,7 +65138,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10">
@@ -64198,7 +65148,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11">
@@ -64250,7 +65200,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d168/2026-2029.xlsx
+++ b/diseases/d168/2026-2029.xlsx
@@ -65022,6 +65022,405 @@
         </is>
       </c>
     </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N364" t="n">
+        <v>0</v>
+      </c>
+      <c r="O364" t="n">
+        <v>0</v>
+      </c>
+      <c r="P364" t="n">
+        <v>0</v>
+      </c>
+      <c r="R364" t="n">
+        <v>0</v>
+      </c>
+      <c r="S364" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO364" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP364" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ364" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS364" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT364" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU364" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV364" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW364" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX364" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY364" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA364" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB364" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC364" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>congenital-rubella-syndrome</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>D168</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>先天性风疹综合征</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N365" t="n">
+        <v>0</v>
+      </c>
+      <c r="O365" t="n">
+        <v>0</v>
+      </c>
+      <c r="P365" t="n">
+        <v>0</v>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V365" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W365" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X365" t="inlineStr">
+        <is>
+          <t>Congenital rubella syndrome</t>
+        </is>
+      </c>
+      <c r="Y365" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z365" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA365" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB365" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC365" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD365" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE365" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF365" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG365" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH365" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI365" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ365" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK365" t="inlineStr">
+        <is>
+          <t>Japan NIID congenital rubella syndrome notifications.</t>
+        </is>
+      </c>
+      <c r="AM365" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN365" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO365" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP365" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ365" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS365" t="inlineStr">
+        <is>
+          <t>SER_JP_CONGENITAL_RUBELLA_SYNDROME_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT365" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU365" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV365" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW365" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX365" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY365" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA365" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB365" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC365" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -65055,7 +65454,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -65138,7 +65537,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -65148,7 +65547,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="11">
@@ -65168,7 +65567,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13">
